--- a/xl/array_calculations.xlsx
+++ b/xl/array_calculations.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11108"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10806"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fz/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felix/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F23A994E-58A4-E149-A652-9FBBB5D5BC6E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CD1E47A-BE2D-EA46-B843-35DFD948B7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3160" yWindow="-18960" windowWidth="28040" windowHeight="17440" xr2:uid="{64832336-0199-7649-B5C2-9B2F3391C2D9}"/>
+    <workbookView xWindow="880" yWindow="780" windowWidth="33300" windowHeight="21360" xr2:uid="{64C9B356-9994-FD48-84B1-3541B8514103}"/>
   </bookViews>
   <sheets>
-    <sheet name="dynamic arrays" sheetId="1" r:id="rId1"/>
-    <sheet name="legacy CSE arrays" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="array1">Sheet1!$A$3:$C$3</definedName>
+    <definedName name="array2">Sheet1!$A$8:$C$9</definedName>
+  </definedNames>
   <calcPr calcId="181029" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -28,6 +31,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -57,35 +62,47 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
-  <si>
-    <t>array2</t>
-  </si>
-  <si>
-    <t>array1</t>
-  </si>
-  <si>
-    <t>array2 + 1</t>
-  </si>
-  <si>
-    <t>array2 * array2</t>
-  </si>
-  <si>
-    <t>array2 * array1</t>
-  </si>
-  <si>
-    <t>array2 @ array2.T</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>• NumPy notation: array2 + 1</t>
+  </si>
+  <si>
+    <t>array1 (Named range)</t>
+  </si>
+  <si>
+    <t>• Excel formula: =array2 + 1</t>
+  </si>
+  <si>
+    <t>• NumPy notation: array2 * array2</t>
+  </si>
+  <si>
+    <t>array2 (Named range)</t>
+  </si>
+  <si>
+    <t>• Excel formula: =array2 * array2</t>
+  </si>
+  <si>
+    <t>• NumPy notation: array2 * array1</t>
+  </si>
+  <si>
+    <t>• Excel formula: =array2 * array1</t>
+  </si>
+  <si>
+    <t>• NumPy notation: array2 @ array2.T</t>
+  </si>
+  <si>
+    <t>• Excel formula: =MMULT(array2, TRANSPOSE(array2))</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -93,9 +110,21 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -106,7 +135,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -114,14 +143,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -150,39 +197,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -234,7 +281,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -345,13 +392,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -360,6 +400,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -424,310 +471,212 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFE12A30-6B83-D949-90DB-878101A66103}">
-  <dimension ref="A1:G15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D993B6E-3857-3347-A33B-FD48950A469C}">
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="10.83203125" style="4"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="22" x14ac:dyDescent="0.3">
+      <c r="D1" s="2"/>
+      <c r="E1" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="22" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="5">
         <v>10</v>
       </c>
-      <c r="B2">
+      <c r="B3" s="5">
         <v>100</v>
       </c>
-      <c r="C2">
+      <c r="C3" s="5">
         <v>1000</v>
       </c>
-      <c r="E2" cm="1">
-        <f t="array" ref="E2:G3">A5:C6 + 1</f>
+      <c r="E3" s="5" cm="1">
+        <f t="array" ref="E3:G4">array2 + 1</f>
         <v>2</v>
       </c>
-      <c r="F2">
+      <c r="F3" s="5">
         <v>3</v>
       </c>
-      <c r="G2">
+      <c r="G3" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E3">
+    <row r="4" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E4" s="5">
         <v>5</v>
       </c>
-      <c r="F3">
+      <c r="F4" s="5">
         <v>6</v>
       </c>
-      <c r="G3">
+      <c r="G4" s="5">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5">
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" ht="22" x14ac:dyDescent="0.3">
+      <c r="E6" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="22" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="E7" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="5">
         <v>1</v>
       </c>
-      <c r="B5">
+      <c r="B8" s="5">
         <v>2</v>
       </c>
-      <c r="C5">
+      <c r="C8" s="5">
         <v>3</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6">
+      <c r="E8" s="5" cm="1">
+        <f t="array" ref="E8:G9">array2 * array2</f>
+        <v>1</v>
+      </c>
+      <c r="F8" s="5">
         <v>4</v>
       </c>
-      <c r="B6">
+      <c r="G8" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="5">
+        <v>4</v>
+      </c>
+      <c r="B9" s="5">
         <v>5</v>
       </c>
-      <c r="C6">
+      <c r="C9" s="5">
         <v>6</v>
       </c>
-      <c r="E6" cm="1">
-        <f t="array" ref="E6:G7">A5:C6 * A5:C6</f>
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
+      <c r="E9" s="5">
+        <v>16</v>
+      </c>
+      <c r="F9" s="5">
+        <v>25</v>
+      </c>
+      <c r="G9" s="5">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="22" x14ac:dyDescent="0.3">
+      <c r="E11" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="22" x14ac:dyDescent="0.3">
+      <c r="E12" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E13" s="5" cm="1">
+        <f t="array" ref="E13:G14">array2 * array1</f>
+        <v>10</v>
+      </c>
+      <c r="F13" s="5">
+        <v>200</v>
+      </c>
+      <c r="G13" s="5">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E14" s="5">
+        <v>40</v>
+      </c>
+      <c r="F14" s="5">
+        <v>500</v>
+      </c>
+      <c r="G14" s="5">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="22" x14ac:dyDescent="0.3">
+      <c r="E16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="5:6" ht="22" x14ac:dyDescent="0.3">
+      <c r="E17" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E7">
-        <v>16</v>
-      </c>
-      <c r="F7">
-        <v>25</v>
-      </c>
-      <c r="G7">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E9" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E10" cm="1">
-        <f t="array" ref="E10:G11">A5:C6 * A2:C2</f>
-        <v>10</v>
-      </c>
-      <c r="F10">
-        <v>200</v>
-      </c>
-      <c r="G10">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E11">
-        <v>40</v>
-      </c>
-      <c r="F11">
-        <v>500</v>
-      </c>
-      <c r="G11">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E13" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E14" cm="1">
-        <f t="array" ref="E14:F15">MMULT(A5:C6, TRANSPOSE(A5:C6))</f>
+    <row r="18" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E18" s="5" cm="1">
+        <f t="array" ref="E18:F19">MMULT(array2, TRANSPOSE(array2))</f>
         <v>14</v>
       </c>
-      <c r="F14">
+      <c r="F18" s="5">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E15">
+    <row r="19" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E19" s="5">
         <v>32</v>
       </c>
-      <c r="F15">
-        <v>77</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8D1A124-6168-3B44-A7BD-C8C3409F009B}">
-  <dimension ref="A1:G15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>10</v>
-      </c>
-      <c r="B2">
-        <v>100</v>
-      </c>
-      <c r="C2">
-        <v>1000</v>
-      </c>
-      <c r="E2">
-        <f t="array" ref="E2:G3">A5:C6 + 1</f>
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E3">
-        <v>5</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <f t="array" ref="E6:G7">A5:C6 * A5:C6</f>
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E7">
-        <v>16</v>
-      </c>
-      <c r="F7">
-        <v>25</v>
-      </c>
-      <c r="G7">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E9" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E10">
-        <f t="array" ref="E10:G11">A5:C6 * A2:C2</f>
-        <v>10</v>
-      </c>
-      <c r="F10">
-        <v>200</v>
-      </c>
-      <c r="G10">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E11">
-        <v>40</v>
-      </c>
-      <c r="F11">
-        <v>500</v>
-      </c>
-      <c r="G11">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E13" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E14">
-        <f t="array" ref="E14:F15">MMULT(A5:C6, TRANSPOSE(A5:C6))</f>
-        <v>14</v>
-      </c>
-      <c r="F14">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E15">
-        <v>32</v>
-      </c>
-      <c r="F15">
+      <c r="F19" s="5">
         <v>77</v>
       </c>
     </row>
